--- a/assets/constructions/examples/ctd_tsmb_radial_doubledir.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_radial_doubledir.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,11 +624,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L060.5-20/K10F</t>
+          <t>R060.6-25/AL41F</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -645,38 +670,34 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PKN</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>PMKNS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M2" t="n">
         <v>0.7</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -688,7 +709,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="V2" t="n">
@@ -701,7 +722,7 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>DUEM_DCON:5</t>
+          <t>DUEM_DCON:6</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -711,12 +732,12 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>K10F</t>
+          <t>AL41F</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
@@ -739,13 +760,32 @@
       <c r="AM2" t="inlineStr">
         <is>
           <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4768.51</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L060.7-20/CN45F</t>
+          <t>L060.3-10/K10F</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -762,39 +802,41 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PMKS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>PKN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.8</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="N3" t="n">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="T3" t="n">
         <v>0.2</v>
@@ -814,7 +856,7 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>DUEM_DCON:7</t>
+          <t>DUEM_DCON:4</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -824,12 +866,12 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>CN45F</t>
+          <t>K10F</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>TIN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
@@ -852,13 +894,32 @@
       <c r="AM3" t="inlineStr">
         <is>
           <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3742.92</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R060.3-10/K10F</t>
+          <t>R060.5-15/CN45F</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -875,41 +936,39 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PKN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>PMKS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.3</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.7</v>
       </c>
-      <c r="M4" t="n">
-        <v>0.4</v>
-      </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="T4" t="n">
         <v>0.2</v>
@@ -929,7 +988,7 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>DUEM_DCON:4</t>
+          <t>DUEM_DCON:5</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -939,12 +998,12 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>K10F</t>
+          <t>CN45F</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>TIN</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
@@ -967,13 +1026,32 @@
       <c r="AM4" t="inlineStr">
         <is>
           <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>45.02</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3956.47</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>PMKS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R060.6-20/AL41F</t>
+          <t>L060.7-20/CN45F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -990,28 +1068,28 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PMKNS</t>
+          <t>PMKS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
         <v>0.7</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="O5" t="n">
         <v>20</v>
@@ -1029,7 +1107,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="V5" t="n">
@@ -1042,7 +1120,7 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>DUEM_DCON:6</t>
+          <t>DUEM_DCON:7</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1052,12 +1130,12 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>AL41F</t>
+          <t>CN45F</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TIN</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -1080,13 +1158,32 @@
       <c r="AM5" t="inlineStr">
         <is>
           <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4791.36</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>PMKS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L060.6-25/K10F</t>
+          <t>R060.3-10/K10F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1112,41 +1209,39 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.4</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="T6" t="n">
         <v>0.2</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="V6" t="n">
@@ -1159,7 +1254,7 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>DUEM_DCON:6</t>
+          <t>DUEM_DCON:4</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1197,6 +1292,25 @@
       <c r="AM6" t="inlineStr">
         <is>
           <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3742.92</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
